--- a/frontend/public/assets/files/Plantilla_Estudiantes.xlsx
+++ b/frontend/public/assets/files/Plantilla_Estudiantes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EMMANUEL\Documents\Proyectos_Programacion\Universidad\SerMedicoUnisimon\PortafolioClinicio\frontend\public\assets\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF8E5ACA-FD2F-4F0E-BD73-C12115AC7869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62A7980D-DF40-48D8-8711-842192700F70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{067AEE59-68B1-4A7C-B281-F61FBFD490FF}"/>
   </bookViews>
@@ -182,20 +182,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -515,53 +510,51 @@
   <dimension ref="A1:H300"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="11.42578125" style="5"/>
+    <col min="1" max="1" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="4" t="s">
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="G1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="4"/>
+      <c r="H1" s="3"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -3546,23 +3539,23 @@
       <c r="H300" s="1"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="dxIcR1aeC19IIdxaY/1DlnlNLLNSiS10/TmJScMXc5RGaH+BED6ImKaNW8g0KojPk83p+pWXwF8msHCNGIdfSw==" saltValue="qovcEgHfc0VXkzwZZp52cQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="FLK+Rqr3rVyGf2JR9PmM8BdkXfXYWb9dv0NyKhbGIBa2/q4UlXcHVC0BMeWjs7TZ3iRBXdrUpVUYb8XYVhel3w==" saltValue="fPnM/6BRUdoTZUJ26RR/Wg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="2">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="G1:H1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F301" xr:uid="{32A1C554-2A09-4351-92E5-C585901FA1FE}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F18:F301 F3:F16" xr:uid="{32A1C554-2A09-4351-92E5-C585901FA1FE}">
       <formula1>1</formula1>
       <formula2>12</formula2>
     </dataValidation>
-    <dataValidation type="custom" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Existen cedulas duplicadas." sqref="A7:A301" xr:uid="{1B7F9B78-6A18-431D-B375-26394CE1F219}">
-      <formula1>COUNTIF($A$3:$A$301,A7)=1</formula1>
-    </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H300" xr:uid="{7FDD554C-12FA-4883-84E9-1FF7E54443E9}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H18:H300 H3:H16" xr:uid="{7FDD554C-12FA-4883-84E9-1FF7E54443E9}">
       <formula1>1</formula1>
       <formula2>2</formula2>
+    </dataValidation>
+    <dataValidation type="custom" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Existen cedulas duplicadas." sqref="A18:A301" xr:uid="{1B7F9B78-6A18-431D-B375-26394CE1F219}">
+      <formula1>COUNTIF($A$4:$A$301,A18)=1</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/frontend/public/assets/files/Plantilla_Estudiantes.xlsx
+++ b/frontend/public/assets/files/Plantilla_Estudiantes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EMMANUEL\Documents\Proyectos_Programacion\Universidad\SerMedicoUnisimon\PortafolioClinicio\frontend\public\assets\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62A7980D-DF40-48D8-8711-842192700F70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D10DF9E9-D0F2-4FD6-91D7-D774E2CD1F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{067AEE59-68B1-4A7C-B281-F61FBFD490FF}"/>
   </bookViews>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="45">
   <si>
     <t>Cedula Estudiante</t>
   </si>
@@ -100,6 +100,111 @@
   </si>
   <si>
     <t>Periodo</t>
+  </si>
+  <si>
+    <t>ANA</t>
+  </si>
+  <si>
+    <t>ISABEL</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>MAYERLIN</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>OSPINO</t>
+  </si>
+  <si>
+    <t>KATERINE</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>DADUL</t>
+  </si>
+  <si>
+    <t>KEREN</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>FLOREZ</t>
+  </si>
+  <si>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>DAVID</t>
+  </si>
+  <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
+    <t>CAROLINA</t>
+  </si>
+  <si>
+    <t>COTES</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>DAVILA</t>
+  </si>
+  <si>
+    <t>NATALIA</t>
+  </si>
+  <si>
+    <t>ANDREA</t>
+  </si>
+  <si>
+    <t>ARCIA</t>
+  </si>
+  <si>
+    <t>JULIO</t>
+  </si>
+  <si>
+    <t>NICOLLE</t>
+  </si>
+  <si>
+    <t>DE LA OSSA</t>
+  </si>
+  <si>
+    <t>FERNANDO</t>
+  </si>
+  <si>
+    <t>JAVIER</t>
+  </si>
+  <si>
+    <t>DE LEON</t>
+  </si>
+  <si>
+    <t>CABALLERO</t>
+  </si>
+  <si>
+    <t>MARIA</t>
+  </si>
+  <si>
+    <t>JOSE</t>
+  </si>
+  <si>
+    <t>SILVA</t>
+  </si>
+  <si>
+    <t>MECLUSKY</t>
   </si>
 </sst>
 </file>
@@ -559,104 +664,256 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
+      <c r="A3" s="1">
+        <v>1639013665</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="1">
+        <v>5</v>
+      </c>
+      <c r="G3" s="1">
+        <v>2026</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
+      <c r="A4" s="1">
+        <v>1529207411</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
+      <c r="D4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="1">
+        <v>5</v>
+      </c>
+      <c r="G4" s="1">
+        <v>2026</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
+      <c r="A5" s="1">
+        <v>1871302957</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
+      <c r="D5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="1">
+        <v>5</v>
+      </c>
+      <c r="G5" s="1">
+        <v>2026</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
+      <c r="A6" s="1">
+        <v>1571886104</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="1">
+        <v>5</v>
+      </c>
+      <c r="G6" s="1">
+        <v>2026</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
+      <c r="A7" s="1">
+        <v>1468830061</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="1">
+        <v>5</v>
+      </c>
+      <c r="G7" s="1">
+        <v>2026</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
+      <c r="A8" s="1">
+        <v>1547074717</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
+      <c r="D8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" s="1">
+        <v>5</v>
+      </c>
+      <c r="G8" s="1">
+        <v>2026</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
+      <c r="A9" s="1">
+        <v>1387114130</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="1">
+        <v>5</v>
+      </c>
+      <c r="G9" s="1">
+        <v>2026</v>
+      </c>
+      <c r="H9" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
+      <c r="A10" s="1">
+        <v>1033770937</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
+      <c r="D10" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10" s="1">
+        <v>5</v>
+      </c>
+      <c r="G10" s="1">
+        <v>2026</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
+      <c r="A11" s="1">
+        <v>1649947460</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="1">
+        <v>5</v>
+      </c>
+      <c r="G11" s="1">
+        <v>2026</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
+      <c r="A12" s="1">
+        <v>1473990517</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F12" s="1">
+        <v>5</v>
+      </c>
+      <c r="G12" s="1">
+        <v>2026</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
